--- a/ig/DM_FINESS_New/ValueSet-jdv-j344-type-act-equipement-materiel-lourd-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j344-type-act-equipement-materiel-lourd-finess.xlsx
@@ -102,7 +102,7 @@
     <t>=</t>
   </si>
   <si>
-    <t>EML</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r374-nature-activite-smsse-regulee|EML</t>
   </si>
   <si>
     <t/>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j344-type-act-equipement-materiel-lourd-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j344-type-act-equipement-materiel-lourd-finess.xlsx
@@ -102,7 +102,7 @@
     <t>=</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r374-nature-activite-smsse-regulee|EML</t>
+    <t>EML</t>
   </si>
   <si>
     <t/>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j344-type-act-equipement-materiel-lourd-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j344-type-act-equipement-materiel-lourd-finess.xlsx
@@ -102,7 +102,7 @@
     <t>=</t>
   </si>
   <si>
-    <t>EML</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r374-nature-activite-smsse-regulee#EML</t>
   </si>
   <si>
     <t/>
